--- a/dev_R/[코드] 데이터 처리/완성본.xlsx
+++ b/dev_R/[코드] 데이터 처리/완성본.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B2708857)</t>
+          <t>B2708857</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>A0114998)</t>
+          <t>A0114998</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -13142,7 +13142,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>A0200224)</t>
+          <t>A0200224</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -16306,7 +16306,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -16871,7 +16871,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -17097,7 +17097,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -18679,7 +18679,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -19357,7 +19357,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -19470,7 +19470,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>A0516251)</t>
+          <t>A0516251</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -19696,7 +19696,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -20487,7 +20487,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -21165,7 +21165,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -21278,7 +21278,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -22295,7 +22295,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -22521,7 +22521,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -22634,7 +22634,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -23086,7 +23086,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -23312,7 +23312,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -23651,7 +23651,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -23764,7 +23764,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -23990,7 +23990,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -24103,7 +24103,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -24329,7 +24329,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -24442,7 +24442,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -24555,7 +24555,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>A2600045)</t>
+          <t>A2600045</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -24781,7 +24781,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -25007,7 +25007,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -25459,7 +25459,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -25572,7 +25572,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -26024,7 +26024,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -26137,7 +26137,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -26250,7 +26250,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -26476,7 +26476,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -26702,7 +26702,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -26815,7 +26815,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -26928,7 +26928,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -27380,7 +27380,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -27493,7 +27493,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -27606,7 +27606,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -27719,7 +27719,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -27832,7 +27832,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -28058,7 +28058,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -28397,7 +28397,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -28510,7 +28510,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -28623,7 +28623,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -28736,7 +28736,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -28849,7 +28849,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>B2503712)</t>
+          <t>B2503712</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
